--- a/ci-cd-merge-resolver/repoCollector/datasets/JSqlParser.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/JSqlParser.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -42,6 +42,42 @@
   </si>
   <si>
     <t>isMultiModule</t>
+  </si>
+  <si>
+    <t>340dcaa9b5a37eee9fb6f59e4bccebc74190d115</t>
+  </si>
+  <si>
+    <t>cfa7e8986c987017eae755b6d3bb183edd5c9f08</t>
+  </si>
+  <si>
+    <t>62bfda765247f410d4dd3c903fa1164e1a2af5ca</t>
+  </si>
+  <si>
+    <t>4da4f13ed2e8d1961357a79ee634440893027945</t>
+  </si>
+  <si>
+    <t>c0801a742c57ea0faaf04bab875d77b10013fd5b</t>
+  </si>
+  <si>
+    <t>572a6c6c915f00274699466a64f7164ba2ccb53e</t>
+  </si>
+  <si>
+    <t>8dd564e973c1ddcc6d399662edc0acdce698dcef</t>
+  </si>
+  <si>
+    <t>403e722e6ee12b408a85947226870a8aaceb6310</t>
+  </si>
+  <si>
+    <t>dbef3a5c834bff97b0701b08241f247ba83feff4</t>
+  </si>
+  <si>
+    <t>e4a91cdb6c7b6250da9680e778853e38e357b332</t>
+  </si>
+  <si>
+    <t>b59b48ec2e7e88a97938aa48aca02809fefe7f00</t>
+  </si>
+  <si>
+    <t>b76e6393db72d62ebfb3817eb069e60a4f73f919</t>
   </si>
   <si>
     <t>8a238f527786633eab6eb6af929b5fe7412a38c6</t>
@@ -140,7 +176,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -186,7 +222,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>942.0</v>
+        <v>685.0</v>
       </c>
       <c r="E2" t="n" s="0">
         <v>1.0</v>
@@ -195,13 +231,13 @@
         <v>1.0</v>
       </c>
       <c r="G2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="b" s="0">
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>50.15900421142578</v>
+        <v>30.375</v>
       </c>
       <c r="J2" t="b" s="0">
         <v>0</v>
@@ -218,7 +254,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>1350.0</v>
+        <v>721.0</v>
       </c>
       <c r="E3" t="n" s="0">
         <v>1.0</v>
@@ -233,7 +269,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>16.233999252319336</v>
+        <v>34.80799102783203</v>
       </c>
       <c r="J3" t="b" s="0">
         <v>0</v>
@@ -250,7 +286,7 @@
         <v>18</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>2114.0</v>
+        <v>668.0</v>
       </c>
       <c r="E4" t="n" s="0">
         <v>1.0</v>
@@ -259,13 +295,13 @@
         <v>1.0</v>
       </c>
       <c r="G4" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="b" s="0">
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>52.515995025634766</v>
+        <v>38.97100067138672</v>
       </c>
       <c r="J4" t="b" s="0">
         <v>0</v>
@@ -282,7 +318,7 @@
         <v>21</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>736.0</v>
+        <v>678.0</v>
       </c>
       <c r="E5" t="n" s="0">
         <v>1.0</v>
@@ -297,7 +333,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>74.43798065185547</v>
+        <v>33.12499237060547</v>
       </c>
       <c r="J5" t="b" s="0">
         <v>0</v>
@@ -314,22 +350,22 @@
         <v>24</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>3045.0</v>
+        <v>942.0</v>
       </c>
       <c r="E6" t="n" s="0">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G6" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b" s="0">
         <v>1</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>73.5890121459961</v>
+        <v>78.65098571777344</v>
       </c>
       <c r="J6" t="b" s="0">
         <v>0</v>
@@ -346,24 +382,152 @@
         <v>27</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>3052.0</v>
+        <v>1423.0</v>
       </c>
       <c r="E7" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F7" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G7" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n" s="0">
+        <v>37.75899887084961</v>
+      </c>
+      <c r="J7" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="D8" t="n" s="0">
+        <v>2114.0</v>
+      </c>
+      <c r="E8" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F8" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G8" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H8" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>72.2619857788086</v>
+      </c>
+      <c r="J8" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D9" t="n" s="0">
+        <v>1367.0</v>
+      </c>
+      <c r="E9" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F9" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G9" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H9" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>101.8010025024414</v>
+      </c>
+      <c r="J9" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="D10" t="n" s="0">
+        <v>3047.0</v>
+      </c>
+      <c r="E10" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="F10" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="G10" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H10" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>92.44499969482422</v>
+      </c>
+      <c r="J10" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="D11" t="n" s="0">
+        <v>3054.0</v>
+      </c>
+      <c r="E11" t="n" s="0">
         <v>5.0</v>
       </c>
-      <c r="F7" t="n" s="0">
+      <c r="F11" t="n" s="0">
         <v>4.0</v>
       </c>
-      <c r="G7" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="H7" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n" s="0">
-        <v>72.7559814453125</v>
-      </c>
-      <c r="J7" t="b" s="0">
+      <c r="G11" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H11" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>94.00898742675781</v>
+      </c>
+      <c r="J11" t="b" s="0">
         <v>0</v>
       </c>
     </row>
